--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/112.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/112.xlsx
@@ -426,13 +426,13 @@
         <v>-11.6683482223801</v>
       </c>
       <c r="E2">
-        <v>-6.370614025958184</v>
+        <v>-9.464992770983462</v>
       </c>
       <c r="F2">
-        <v>-4.764494371509473</v>
+        <v>-4.855981102979621</v>
       </c>
       <c r="G2">
-        <v>-16.98989300657611</v>
+        <v>-16.09568982732742</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.82071141953045</v>
       </c>
       <c r="E3">
-        <v>-7.651687623410075</v>
+        <v>-8.003586281598123</v>
       </c>
       <c r="F3">
-        <v>-5.215339812251987</v>
+        <v>-4.475709557093879</v>
       </c>
       <c r="G3">
-        <v>-16.74617064397496</v>
+        <v>-17.01305689371439</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.00105635877104</v>
       </c>
       <c r="E4">
-        <v>-7.99828343853514</v>
+        <v>-8.705721648013403</v>
       </c>
       <c r="F4">
-        <v>-4.744275989940015</v>
+        <v>-4.796860569303309</v>
       </c>
       <c r="G4">
-        <v>-16.51958200981232</v>
+        <v>-16.07814393596928</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.310163636972081</v>
       </c>
       <c r="E5">
-        <v>-6.871997611139431</v>
+        <v>-10.09797381082761</v>
       </c>
       <c r="F5">
-        <v>-4.548485595026068</v>
+        <v>-4.061448514850974</v>
       </c>
       <c r="G5">
-        <v>-16.86118065128201</v>
+        <v>-17.04749649895943</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.698148745333</v>
       </c>
       <c r="E6">
-        <v>-9.343942132284425</v>
+        <v>-12.3079008258888</v>
       </c>
       <c r="F6">
-        <v>-4.417391170463737</v>
+        <v>-3.982893534033347</v>
       </c>
       <c r="G6">
-        <v>-16.73244677744191</v>
+        <v>-17.31351207522203</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.155703408196176</v>
       </c>
       <c r="E7">
-        <v>-10.91192172896628</v>
+        <v>-12.15719773938754</v>
       </c>
       <c r="F7">
-        <v>-4.539288222922153</v>
+        <v>-4.218899765111006</v>
       </c>
       <c r="G7">
-        <v>-16.74305873116805</v>
+        <v>-16.50360531703979</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.633497138861411</v>
       </c>
       <c r="E8">
-        <v>-10.75392779931267</v>
+        <v>-13.24076194299488</v>
       </c>
       <c r="F8">
-        <v>-3.908103814029677</v>
+        <v>-3.377840272745621</v>
       </c>
       <c r="G8">
-        <v>-16.65881527883021</v>
+        <v>-15.49938443315727</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.110047847320017</v>
       </c>
       <c r="E9">
-        <v>-11.959692874017</v>
+        <v>-13.39440853760113</v>
       </c>
       <c r="F9">
-        <v>-3.749660372013622</v>
+        <v>-3.683752074783736</v>
       </c>
       <c r="G9">
-        <v>-15.49606230070861</v>
+        <v>-16.98628285666553</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.55275413630551</v>
       </c>
       <c r="E10">
-        <v>-14.08934815881822</v>
+        <v>-14.29252267364636</v>
       </c>
       <c r="F10">
-        <v>-4.066942390671634</v>
+        <v>-3.532847072925173</v>
       </c>
       <c r="G10">
-        <v>-15.72881351539261</v>
+        <v>-17.0211627644673</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.947905893798595</v>
       </c>
       <c r="E11">
-        <v>-13.66158850405368</v>
+        <v>-14.71625651501808</v>
       </c>
       <c r="F11">
-        <v>-3.35550130895539</v>
+        <v>-3.5424150322133</v>
       </c>
       <c r="G11">
-        <v>-16.05456623063859</v>
+        <v>-14.96979480796729</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.299107940786516</v>
       </c>
       <c r="E12">
-        <v>-14.10366719363048</v>
+        <v>-15.33840997350989</v>
       </c>
       <c r="F12">
-        <v>-3.494661547745054</v>
+        <v>-3.10995958456087</v>
       </c>
       <c r="G12">
-        <v>-16.04730785954374</v>
+        <v>-16.16102840936324</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.615138542220012</v>
       </c>
       <c r="E13">
-        <v>-14.91229868328414</v>
+        <v>-16.27078201542315</v>
       </c>
       <c r="F13">
-        <v>-3.314758890574795</v>
+        <v>-3.552616473867603</v>
       </c>
       <c r="G13">
-        <v>-15.54489450268563</v>
+        <v>-17.27921813398071</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.932427822284227</v>
       </c>
       <c r="E14">
-        <v>-16.07654217981215</v>
+        <v>-16.59710385241588</v>
       </c>
       <c r="F14">
-        <v>-3.012603638968103</v>
+        <v>-3.865582893906043</v>
       </c>
       <c r="G14">
-        <v>-15.06134794485584</v>
+        <v>-15.52060999588231</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.285620777303623</v>
       </c>
       <c r="E15">
-        <v>-16.00853355716495</v>
+        <v>-17.78166208334229</v>
       </c>
       <c r="F15">
-        <v>-2.925483184706821</v>
+        <v>-2.873165459790279</v>
       </c>
       <c r="G15">
-        <v>-14.63458220884285</v>
+        <v>-14.12409939723277</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.718742293225183</v>
       </c>
       <c r="E16">
-        <v>-16.71127121062325</v>
+        <v>-19.92326801104975</v>
       </c>
       <c r="F16">
-        <v>-2.220498080154866</v>
+        <v>-2.25316043095489</v>
       </c>
       <c r="G16">
-        <v>-14.56810645441428</v>
+        <v>-13.52345387786064</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.274763613706515</v>
       </c>
       <c r="E17">
-        <v>-18.3078209498195</v>
+        <v>-19.88321365845191</v>
       </c>
       <c r="F17">
-        <v>-2.651687354927903</v>
+        <v>-2.174845381583451</v>
       </c>
       <c r="G17">
-        <v>-13.66832997175023</v>
+        <v>-12.65989145285067</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.980062553555337</v>
       </c>
       <c r="E18">
-        <v>-19.27527055139617</v>
+        <v>-20.99599557635675</v>
       </c>
       <c r="F18">
-        <v>-2.284418034607918</v>
+        <v>-2.163228898693703</v>
       </c>
       <c r="G18">
-        <v>-12.3951504366207</v>
+        <v>-12.2149607534637</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.85840316251611</v>
       </c>
       <c r="E19">
-        <v>-20.42244170091526</v>
+        <v>-21.87015861337541</v>
       </c>
       <c r="F19">
-        <v>-1.638816358914239</v>
+        <v>-1.545220131164725</v>
       </c>
       <c r="G19">
-        <v>-12.17651869866169</v>
+        <v>-14.22156020263614</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.906131629676446</v>
       </c>
       <c r="E20">
-        <v>-21.62896303077887</v>
+        <v>-23.52515736658865</v>
       </c>
       <c r="F20">
-        <v>-1.227965827360233</v>
+        <v>-1.706352705825196</v>
       </c>
       <c r="G20">
-        <v>-11.37176149406579</v>
+        <v>-12.63085465792573</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.110998926051519</v>
       </c>
       <c r="E21">
-        <v>-22.6765032236552</v>
+        <v>-23.05779620662704</v>
       </c>
       <c r="F21">
-        <v>-1.40529971353565</v>
+        <v>-1.564972111342086</v>
       </c>
       <c r="G21">
-        <v>-11.9228878732615</v>
+        <v>-13.05881550087839</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.443417918828938</v>
       </c>
       <c r="E22">
-        <v>-21.97583961129241</v>
+        <v>-22.21132478816528</v>
       </c>
       <c r="F22">
-        <v>-1.246442924275665</v>
+        <v>-0.6913326208842805</v>
       </c>
       <c r="G22">
-        <v>-11.73546464810121</v>
+        <v>-11.60060957555899</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.86083080751742</v>
       </c>
       <c r="E23">
-        <v>-23.40059716053367</v>
+        <v>-24.65224020540971</v>
       </c>
       <c r="F23">
-        <v>-0.9184463432467476</v>
+        <v>-0.7254464381558039</v>
       </c>
       <c r="G23">
-        <v>-11.6050192222173</v>
+        <v>-12.00508209791053</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.3218904949891</v>
       </c>
       <c r="E24">
-        <v>-22.20192367612535</v>
+        <v>-25.87541273419953</v>
       </c>
       <c r="F24">
-        <v>-0.939211103357032</v>
+        <v>-0.7534028068280988</v>
       </c>
       <c r="G24">
-        <v>-11.52951561010314</v>
+        <v>-12.56342877692739</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.778109931317186</v>
       </c>
       <c r="E25">
-        <v>-24.35881320360871</v>
+        <v>-26.2424953657353</v>
       </c>
       <c r="F25">
-        <v>-0.961767826710636</v>
+        <v>-0.3639552688682997</v>
       </c>
       <c r="G25">
-        <v>-11.51468436608721</v>
+        <v>-12.66179170599021</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.196125380092053</v>
       </c>
       <c r="E26">
-        <v>-23.71355547072977</v>
+        <v>-25.09823602500315</v>
       </c>
       <c r="F26">
-        <v>-0.5327308082766816</v>
+        <v>0.0399808026588972</v>
       </c>
       <c r="G26">
-        <v>-11.92430478675231</v>
+        <v>-13.11860395331763</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.548711978791508</v>
       </c>
       <c r="E27">
-        <v>-23.14259188242066</v>
+        <v>-25.1181069689488</v>
       </c>
       <c r="F27">
-        <v>-0.6555511612837993</v>
+        <v>-0.3069996611783931</v>
       </c>
       <c r="G27">
-        <v>-12.41549042841398</v>
+        <v>-11.81452709667008</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.821598581770158</v>
       </c>
       <c r="E28">
-        <v>-25.08517590596503</v>
+        <v>-25.68713237038262</v>
       </c>
       <c r="F28">
-        <v>-0.7957946549196242</v>
+        <v>-0.1148509980169981</v>
       </c>
       <c r="G28">
-        <v>-11.68957386583583</v>
+        <v>-12.64603681976882</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.011681312102628</v>
       </c>
       <c r="E29">
-        <v>-23.70881415844374</v>
+        <v>-27.93227279932746</v>
       </c>
       <c r="F29">
-        <v>-0.4363456744100791</v>
+        <v>-0.03663255470640151</v>
       </c>
       <c r="G29">
-        <v>-11.9615053869771</v>
+        <v>-13.6289891038343</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.117192378064262</v>
       </c>
       <c r="E30">
-        <v>-23.94966557701569</v>
+        <v>-25.88540254786045</v>
       </c>
       <c r="F30">
-        <v>-0.6036483673171024</v>
+        <v>-0.3216140993660683</v>
       </c>
       <c r="G30">
-        <v>-12.65843481281339</v>
+        <v>-11.91311514282958</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.146043043492099</v>
       </c>
       <c r="E31">
-        <v>-23.28100469046511</v>
+        <v>-24.69038354197632</v>
       </c>
       <c r="F31">
-        <v>-0.5036112076094964</v>
+        <v>0.2198359486516935</v>
       </c>
       <c r="G31">
-        <v>-12.5708311567532</v>
+        <v>-13.40903149238681</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.105474895038427</v>
       </c>
       <c r="E32">
-        <v>-23.36470447554888</v>
+        <v>-25.16281659282653</v>
       </c>
       <c r="F32">
-        <v>-0.4430209948436564</v>
+        <v>0.5614603190829676</v>
       </c>
       <c r="G32">
-        <v>-11.72240785649432</v>
+        <v>-11.49335452117768</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.008078937322842</v>
       </c>
       <c r="E33">
-        <v>-23.68079648975828</v>
+        <v>-25.68822373261847</v>
       </c>
       <c r="F33">
-        <v>-0.4980278524046147</v>
+        <v>-0.03490631525857251</v>
       </c>
       <c r="G33">
-        <v>-10.7935846472687</v>
+        <v>-11.99071101972455</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.869923341915629</v>
       </c>
       <c r="E34">
-        <v>-23.14672185071566</v>
+        <v>-24.72536600368558</v>
       </c>
       <c r="F34">
-        <v>-0.7224714465936509</v>
+        <v>-0.4064389719029206</v>
       </c>
       <c r="G34">
-        <v>-12.12948577818526</v>
+        <v>-13.41830101989677</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.702995933121947</v>
       </c>
       <c r="E35">
-        <v>-22.77875163827439</v>
+        <v>-24.21520170740346</v>
       </c>
       <c r="F35">
-        <v>-0.7763800041022519</v>
+        <v>-0.4312334717150406</v>
       </c>
       <c r="G35">
-        <v>-10.7314225336778</v>
+        <v>-12.07250135781779</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.524711410488172</v>
       </c>
       <c r="E36">
-        <v>-21.487937293232</v>
+        <v>-24.65751587762865</v>
       </c>
       <c r="F36">
-        <v>-0.5363772911469809</v>
+        <v>-0.9309425747725225</v>
       </c>
       <c r="G36">
-        <v>-11.81707621673532</v>
+        <v>-11.91849146878535</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.346612335937331</v>
       </c>
       <c r="E37">
-        <v>-21.40612588180943</v>
+        <v>-24.92473660034727</v>
       </c>
       <c r="F37">
-        <v>-0.616235661933015</v>
+        <v>-0.8904986849569877</v>
       </c>
       <c r="G37">
-        <v>-11.15603310454473</v>
+        <v>-12.63466178529589</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.179830385719455</v>
       </c>
       <c r="E38">
-        <v>-21.19236832322536</v>
+        <v>-24.95441621899354</v>
       </c>
       <c r="F38">
-        <v>-0.9299028718390365</v>
+        <v>-0.6312381080699729</v>
       </c>
       <c r="G38">
-        <v>-10.67310065291246</v>
+        <v>-11.41719211050121</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.035003094315403</v>
       </c>
       <c r="E39">
-        <v>-20.36603050020171</v>
+        <v>-22.57364799351899</v>
       </c>
       <c r="F39">
-        <v>-0.8136105546153602</v>
+        <v>-0.1180413735836509</v>
       </c>
       <c r="G39">
-        <v>-11.45478997619071</v>
+        <v>-10.57628705916202</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.913841645946926</v>
       </c>
       <c r="E40">
-        <v>-20.64876577487061</v>
+        <v>-22.19065230432026</v>
       </c>
       <c r="F40">
-        <v>-0.9194488290912207</v>
+        <v>-0.4162516137549834</v>
       </c>
       <c r="G40">
-        <v>-10.44986063556279</v>
+        <v>-11.52883032717651</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.821959804311023</v>
       </c>
       <c r="E41">
-        <v>-18.92817207565625</v>
+        <v>-21.71096916658377</v>
       </c>
       <c r="F41">
-        <v>-1.059071510008193</v>
+        <v>-0.3276298062858651</v>
       </c>
       <c r="G41">
-        <v>-10.97509523809586</v>
+        <v>-12.14344303817883</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.756324657883754</v>
       </c>
       <c r="E42">
-        <v>-18.83887962517301</v>
+        <v>-21.54363752352635</v>
       </c>
       <c r="F42">
-        <v>-1.425646375284258</v>
+        <v>-0.3405948147626101</v>
       </c>
       <c r="G42">
-        <v>-9.919014658340654</v>
+        <v>-12.07240866254269</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.716010049375386</v>
       </c>
       <c r="E43">
-        <v>-17.7914118878808</v>
+        <v>-20.95424304600603</v>
       </c>
       <c r="F43">
-        <v>-1.397935481028856</v>
+        <v>-0.9597921535811252</v>
       </c>
       <c r="G43">
-        <v>-9.239707266409903</v>
+        <v>-10.1133800974968</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.700895425912757</v>
       </c>
       <c r="E44">
-        <v>-18.07115836970464</v>
+        <v>-20.77729745263031</v>
       </c>
       <c r="F44">
-        <v>-1.567615316514954</v>
+        <v>-1.095339959177672</v>
       </c>
       <c r="G44">
-        <v>-9.907192700219916</v>
+        <v>-9.894023350064696</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.704093262028514</v>
       </c>
       <c r="E45">
-        <v>-17.95738951720994</v>
+        <v>-19.76992029572801</v>
       </c>
       <c r="F45">
-        <v>-1.643907973432376</v>
+        <v>-0.7911773603231604</v>
       </c>
       <c r="G45">
-        <v>-10.0193606041815</v>
+        <v>-10.36053549582217</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.724690951418141</v>
       </c>
       <c r="E46">
-        <v>-16.55296028778911</v>
+        <v>-19.84611639938107</v>
       </c>
       <c r="F46">
-        <v>-2.00674687645392</v>
+        <v>-0.3711635063424223</v>
       </c>
       <c r="G46">
-        <v>-9.53574618016815</v>
+        <v>-9.878937194042237</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.752418379646119</v>
       </c>
       <c r="E47">
-        <v>-15.84330765452109</v>
+        <v>-21.02811151401914</v>
       </c>
       <c r="F47">
-        <v>-1.6182511457493</v>
+        <v>-1.143281904649855</v>
       </c>
       <c r="G47">
-        <v>-9.895493232284132</v>
+        <v>-10.49152716172006</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.780002199862946</v>
       </c>
       <c r="E48">
-        <v>-14.32762740415382</v>
+        <v>-19.80253889400526</v>
       </c>
       <c r="F48">
-        <v>-2.026209830301713</v>
+        <v>-1.226054294320298</v>
       </c>
       <c r="G48">
-        <v>-9.795316124265787</v>
+        <v>-11.53481579351152</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.803632191184839</v>
       </c>
       <c r="E49">
-        <v>-16.17428929126771</v>
+        <v>-16.80232976596949</v>
       </c>
       <c r="F49">
-        <v>-1.955243176377913</v>
+        <v>-1.865259381821517</v>
       </c>
       <c r="G49">
-        <v>-9.522206048912532</v>
+        <v>-10.30146212121942</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.820598085686745</v>
       </c>
       <c r="E50">
-        <v>-15.1885718255441</v>
+        <v>-18.29864626147996</v>
       </c>
       <c r="F50">
-        <v>-2.114102341196771</v>
+        <v>-1.886499253706433</v>
       </c>
       <c r="G50">
-        <v>-9.688981401544396</v>
+        <v>-10.76641168948236</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.841630389697734</v>
       </c>
       <c r="E51">
-        <v>-13.2811559311433</v>
+        <v>-17.85575244658178</v>
       </c>
       <c r="F51">
-        <v>-2.29948145342262</v>
+        <v>-1.558082198756967</v>
       </c>
       <c r="G51">
-        <v>-9.197815623155964</v>
+        <v>-10.74866716539187</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.872271213492723</v>
       </c>
       <c r="E52">
-        <v>-12.45785671417879</v>
+        <v>-15.87148381979682</v>
       </c>
       <c r="F52">
-        <v>-2.594274056228434</v>
+        <v>-1.902417081862515</v>
       </c>
       <c r="G52">
-        <v>-8.891070405123715</v>
+        <v>-9.555801465045056</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.92548226523037</v>
       </c>
       <c r="E53">
-        <v>-12.80411289375328</v>
+        <v>-16.0907434743002</v>
       </c>
       <c r="F53">
-        <v>-2.648331482093087</v>
+        <v>-1.830187422471153</v>
       </c>
       <c r="G53">
-        <v>-9.925695339238903</v>
+        <v>-9.513836989789253</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.008935312936496</v>
       </c>
       <c r="E54">
-        <v>-13.10639306223929</v>
+        <v>-15.95668252977713</v>
       </c>
       <c r="F54">
-        <v>-2.722537606466918</v>
+        <v>-0.7613284630819155</v>
       </c>
       <c r="G54">
-        <v>-9.778071492551723</v>
+        <v>-10.16893436219132</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.12646161223917</v>
       </c>
       <c r="E55">
-        <v>-12.92102903568332</v>
+        <v>-15.14619436578032</v>
       </c>
       <c r="F55">
-        <v>-2.44302222277439</v>
+        <v>-2.749507326353894</v>
       </c>
       <c r="G55">
-        <v>-9.232016869122177</v>
+        <v>-8.951487861215414</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.284089334684357</v>
       </c>
       <c r="E56">
-        <v>-10.77439650182734</v>
+        <v>-14.58927810384301</v>
       </c>
       <c r="F56">
-        <v>-2.574437347784598</v>
+        <v>-2.061897059400225</v>
       </c>
       <c r="G56">
-        <v>-9.544780658944822</v>
+        <v>-9.841117521801603</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.477791660733294</v>
       </c>
       <c r="E57">
-        <v>-10.7335813655962</v>
+        <v>-12.28055337135648</v>
       </c>
       <c r="F57">
-        <v>-2.91373208681426</v>
+        <v>-2.64802503499845</v>
       </c>
       <c r="G57">
-        <v>-8.953166307803825</v>
+        <v>-10.00232122629087</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.707556217179592</v>
       </c>
       <c r="E58">
-        <v>-10.58862038413667</v>
+        <v>-13.93014965507857</v>
       </c>
       <c r="F58">
-        <v>-2.906253827481555</v>
+        <v>-2.46960155915321</v>
       </c>
       <c r="G58">
-        <v>-9.348200464822899</v>
+        <v>-10.80254298349797</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.962786946334114</v>
       </c>
       <c r="E59">
-        <v>-10.07319400105764</v>
+        <v>-12.39869672974259</v>
       </c>
       <c r="F59">
-        <v>-2.57431144316432</v>
+        <v>-2.910529833453242</v>
       </c>
       <c r="G59">
-        <v>-9.257299505405589</v>
+        <v>-9.786586215678728</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.232211177336667</v>
       </c>
       <c r="E60">
-        <v>-9.00673384377726</v>
+        <v>-13.1073440417809</v>
       </c>
       <c r="F60">
-        <v>-2.933546623375281</v>
+        <v>-2.414755447742669</v>
       </c>
       <c r="G60">
-        <v>-9.539950573003024</v>
+        <v>-10.58832089219727</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.509111497056203</v>
       </c>
       <c r="E61">
-        <v>-10.35740555825304</v>
+        <v>-12.61152142268107</v>
       </c>
       <c r="F61">
-        <v>-2.649298334554463</v>
+        <v>-2.680659670944952</v>
       </c>
       <c r="G61">
-        <v>-9.837826839535568</v>
+        <v>-10.60573436173383</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.780357492662376</v>
       </c>
       <c r="E62">
-        <v>-7.274588007369341</v>
+        <v>-10.39818446669211</v>
       </c>
       <c r="F62">
-        <v>-2.964971308002388</v>
+        <v>-2.60453013573682</v>
       </c>
       <c r="G62">
-        <v>-9.677447460885574</v>
+        <v>-10.53430272063298</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.043762149902554</v>
       </c>
       <c r="E63">
-        <v>-8.28941450401426</v>
+        <v>-13.01638964133684</v>
       </c>
       <c r="F63">
-        <v>-3.114443847860437</v>
+        <v>-2.828882666835719</v>
       </c>
       <c r="G63">
-        <v>-9.964557833324408</v>
+        <v>-10.90397809882124</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.290697871206421</v>
       </c>
       <c r="E64">
-        <v>-7.699530951301112</v>
+        <v>-12.96433483261867</v>
       </c>
       <c r="F64">
-        <v>-3.079131165210925</v>
+        <v>-2.69242581404371</v>
       </c>
       <c r="G64">
-        <v>-10.34303595210159</v>
+        <v>-11.14438329479203</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.515420490859324</v>
       </c>
       <c r="E65">
-        <v>-7.853064334057168</v>
+        <v>-12.59810355419634</v>
       </c>
       <c r="F65">
-        <v>-3.119164083341404</v>
+        <v>-2.825385052321471</v>
       </c>
       <c r="G65">
-        <v>-9.245702664381524</v>
+        <v>-11.52772129442086</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.712441422437149</v>
       </c>
       <c r="E66">
-        <v>-7.013761489949552</v>
+        <v>-7.996336194711843</v>
       </c>
       <c r="F66">
-        <v>-3.746056649203039</v>
+        <v>-2.531941766955611</v>
       </c>
       <c r="G66">
-        <v>-9.902339440459345</v>
+        <v>-11.06434754583461</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.865700608472551</v>
       </c>
       <c r="E67">
-        <v>-7.387206627466095</v>
+        <v>-11.11800352410734</v>
       </c>
       <c r="F67">
-        <v>-3.552651315397743</v>
+        <v>-3.083935337105411</v>
       </c>
       <c r="G67">
-        <v>-10.15489102801373</v>
+        <v>-10.99882191797582</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.965659921312325</v>
       </c>
       <c r="E68">
-        <v>-7.02451208724376</v>
+        <v>-10.4117563032931</v>
       </c>
       <c r="F68">
-        <v>-3.581764581241266</v>
+        <v>-3.21566957885758</v>
       </c>
       <c r="G68">
-        <v>-10.61529852779679</v>
+        <v>-10.68402545319206</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.998486338023221</v>
       </c>
       <c r="E69">
-        <v>-7.606484395865509</v>
+        <v>-10.58158766400276</v>
       </c>
       <c r="F69">
-        <v>-3.534264489719491</v>
+        <v>-3.058688689254433</v>
       </c>
       <c r="G69">
-        <v>-10.31524723284494</v>
+        <v>-11.21347769074216</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.956526850946076</v>
       </c>
       <c r="E70">
-        <v>-7.657932389066652</v>
+        <v>-11.04555246845862</v>
       </c>
       <c r="F70">
-        <v>-3.178220476928141</v>
+        <v>-2.850557265994423</v>
       </c>
       <c r="G70">
-        <v>-10.26946569858236</v>
+        <v>-10.42917634703342</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.840351007919711</v>
       </c>
       <c r="E71">
-        <v>-7.109710797224071</v>
+        <v>-8.918356145043566</v>
       </c>
       <c r="F71">
-        <v>-3.160990548421117</v>
+        <v>-2.82406582529391</v>
       </c>
       <c r="G71">
-        <v>-10.04494781065453</v>
+        <v>-10.18482829132536</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.649449982840201</v>
       </c>
       <c r="E72">
-        <v>-7.370098052665116</v>
+        <v>-10.94063225417491</v>
       </c>
       <c r="F72">
-        <v>-3.978467867852651</v>
+        <v>-3.214435080096495</v>
       </c>
       <c r="G72">
-        <v>-9.555477031582207</v>
+        <v>-11.01008108335488</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.395753241916832</v>
       </c>
       <c r="E73">
-        <v>-8.036861508606485</v>
+        <v>-11.10324522731634</v>
       </c>
       <c r="F73">
-        <v>-3.975996494771608</v>
+        <v>-3.511501092743922</v>
       </c>
       <c r="G73">
-        <v>-9.002374256699552</v>
+        <v>-9.35750309778825</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.089061826154254</v>
       </c>
       <c r="E74">
-        <v>-7.756571609901727</v>
+        <v>-11.90588101738385</v>
       </c>
       <c r="F74">
-        <v>-3.915411824976472</v>
+        <v>-3.239983423924364</v>
       </c>
       <c r="G74">
-        <v>-9.646106526265294</v>
+        <v>-9.01627854796449</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.743541657376045</v>
       </c>
       <c r="E75">
-        <v>-8.303932791682852</v>
+        <v>-11.73376730577433</v>
       </c>
       <c r="F75">
-        <v>-4.163648224986113</v>
+        <v>-3.637074718485031</v>
       </c>
       <c r="G75">
-        <v>-8.804701582549669</v>
+        <v>-10.70902007201355</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.377848260683431</v>
       </c>
       <c r="E76">
-        <v>-7.97367571077746</v>
+        <v>-11.91177709054184</v>
       </c>
       <c r="F76">
-        <v>-4.436763061221392</v>
+        <v>-3.915708769835617</v>
       </c>
       <c r="G76">
-        <v>-8.327877087437361</v>
+        <v>-10.18753962812202</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.003863786838515</v>
       </c>
       <c r="E77">
-        <v>-9.364831982881809</v>
+        <v>-11.89821431088887</v>
       </c>
       <c r="F77">
-        <v>-4.230693623063284</v>
+        <v>-4.002177529112696</v>
       </c>
       <c r="G77">
-        <v>-8.62709081436777</v>
+        <v>-8.950656914285057</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.642629249399517</v>
       </c>
       <c r="E78">
-        <v>-10.77357684803195</v>
+        <v>-12.53644838058191</v>
       </c>
       <c r="F78">
-        <v>-4.450401936565156</v>
+        <v>-3.95504564921626</v>
       </c>
       <c r="G78">
-        <v>-8.388188606071804</v>
+        <v>-9.487266551291063</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.306460545823556</v>
       </c>
       <c r="E79">
-        <v>-10.04088333901291</v>
+        <v>-12.4193103434255</v>
       </c>
       <c r="F79">
-        <v>-4.319937035104212</v>
+        <v>-3.806005461073126</v>
       </c>
       <c r="G79">
-        <v>-8.879129267363563</v>
+        <v>-9.893477110050716</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.009751482266087</v>
       </c>
       <c r="E80">
-        <v>-11.70649683530014</v>
+        <v>-14.67808600760743</v>
       </c>
       <c r="F80">
-        <v>-4.844285434794101</v>
+        <v>-4.117514079816404</v>
       </c>
       <c r="G80">
-        <v>-8.116641108213084</v>
+        <v>-8.678738635325939</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.766086754349036</v>
       </c>
       <c r="E81">
-        <v>-11.12644007118363</v>
+        <v>-12.84791229435547</v>
       </c>
       <c r="F81">
-        <v>-4.359902645733285</v>
+        <v>-4.236544624567875</v>
       </c>
       <c r="G81">
-        <v>-7.408972272647397</v>
+        <v>-9.674885098638178</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.579150353836969</v>
       </c>
       <c r="E82">
-        <v>-11.57629867910561</v>
+        <v>-14.1587062667197</v>
       </c>
       <c r="F82">
-        <v>-5.117978323688516</v>
+        <v>-4.46863514276961</v>
       </c>
       <c r="G82">
-        <v>-7.868787184778929</v>
+        <v>-8.83790635430856</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.461350875100477</v>
       </c>
       <c r="E83">
-        <v>-12.66403813574803</v>
+        <v>-14.17536652259392</v>
       </c>
       <c r="F83">
-        <v>-5.0817779738734</v>
+        <v>-4.877361132838054</v>
       </c>
       <c r="G83">
-        <v>-7.714217813550357</v>
+        <v>-8.891212758581904</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.412358570011314</v>
       </c>
       <c r="E84">
-        <v>-13.81152627844765</v>
+        <v>-14.76422211170733</v>
       </c>
       <c r="F84">
-        <v>-4.77964647785544</v>
+        <v>-4.687018686273218</v>
       </c>
       <c r="G84">
-        <v>-7.541331193852998</v>
+        <v>-9.902216950274392</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.43824323443287</v>
       </c>
       <c r="E85">
-        <v>-13.5552101211395</v>
+        <v>-17.32687649569997</v>
       </c>
       <c r="F85">
-        <v>-5.78881714499768</v>
+        <v>-4.765705114681826</v>
       </c>
       <c r="G85">
-        <v>-7.853697718210931</v>
+        <v>-8.726830930374932</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.540356029731219</v>
       </c>
       <c r="E86">
-        <v>-16.19691807588404</v>
+        <v>-17.95940015966934</v>
       </c>
       <c r="F86">
-        <v>-5.200051507197291</v>
+        <v>-4.524661115087154</v>
       </c>
       <c r="G86">
-        <v>-7.827402054992501</v>
+        <v>-9.227497974461071</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.71534036858146</v>
       </c>
       <c r="E87">
-        <v>-16.84579858796912</v>
+        <v>-19.66433439576517</v>
       </c>
       <c r="F87">
-        <v>-5.465982653400138</v>
+        <v>-4.612670028366997</v>
       </c>
       <c r="G87">
-        <v>-7.076255824859564</v>
+        <v>-8.89681751217989</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.96790560628854</v>
       </c>
       <c r="E88">
-        <v>-18.30422986993142</v>
+        <v>-20.7272804572156</v>
       </c>
       <c r="F88">
-        <v>-5.641123898735628</v>
+        <v>-5.278008639031841</v>
       </c>
       <c r="G88">
-        <v>-6.739904398069612</v>
+        <v>-8.270167657596787</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.289124629645325</v>
       </c>
       <c r="E89">
-        <v>-20.07070606779148</v>
+        <v>-21.96700908697746</v>
       </c>
       <c r="F89">
-        <v>-6.198098619915964</v>
+        <v>-4.774935744609966</v>
       </c>
       <c r="G89">
-        <v>-8.510662238297142</v>
+        <v>-8.484416233261799</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.684624257322263</v>
       </c>
       <c r="E90">
-        <v>-21.58699766214979</v>
+        <v>-24.11543489654047</v>
       </c>
       <c r="F90">
-        <v>-5.917253319180946</v>
+        <v>-4.997197783900484</v>
       </c>
       <c r="G90">
-        <v>-7.533048208913742</v>
+        <v>-8.651804036818429</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.150979169676002</v>
       </c>
       <c r="E91">
-        <v>-23.56417922711275</v>
+        <v>-25.36186566783368</v>
       </c>
       <c r="F91">
-        <v>-5.77777792291411</v>
+        <v>-5.045314728876323</v>
       </c>
       <c r="G91">
-        <v>-7.742155507356268</v>
+        <v>-9.388330897849944</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.688044484793881</v>
       </c>
       <c r="E92">
-        <v>-24.57272020183503</v>
+        <v>-27.26893286973589</v>
       </c>
       <c r="F92">
-        <v>-6.085690737376382</v>
+        <v>-5.43784336669461</v>
       </c>
       <c r="G92">
-        <v>-8.475540660671014</v>
+        <v>-9.18258049258424</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.301358697743169</v>
       </c>
       <c r="E93">
-        <v>-27.76076137476095</v>
+        <v>-29.66044942826765</v>
       </c>
       <c r="F93">
-        <v>-5.737774303343067</v>
+        <v>-4.85298473138761</v>
       </c>
       <c r="G93">
-        <v>-8.361548646117289</v>
+        <v>-9.671935402562688</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.981462446156372</v>
       </c>
       <c r="E94">
-        <v>-28.58138879206093</v>
+        <v>-29.73731574607385</v>
       </c>
       <c r="F94">
-        <v>-5.628404364675776</v>
+        <v>-5.148753688890293</v>
       </c>
       <c r="G94">
-        <v>-8.381772768816695</v>
+        <v>-8.953497362357751</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.734027086720152</v>
       </c>
       <c r="E95">
-        <v>-30.90626206285882</v>
+        <v>-30.77204035750847</v>
       </c>
       <c r="F95">
-        <v>-5.850873869441218</v>
+        <v>-4.098107347528609</v>
       </c>
       <c r="G95">
-        <v>-9.393905856538076</v>
+        <v>-10.67834124650113</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.553425124573073</v>
       </c>
       <c r="E96">
-        <v>-32.8973890635284</v>
+        <v>-34.40721626124076</v>
       </c>
       <c r="F96">
-        <v>-5.484283167105998</v>
+        <v>-4.686959297301389</v>
       </c>
       <c r="G96">
-        <v>-8.660812031230787</v>
+        <v>-9.351587152909573</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.422605652223831</v>
       </c>
       <c r="E97">
-        <v>-35.4757232887726</v>
+        <v>-36.83826639785948</v>
       </c>
       <c r="F97">
-        <v>-5.309702553664573</v>
+        <v>-4.426932206751301</v>
       </c>
       <c r="G97">
-        <v>-9.604767744116415</v>
+        <v>-10.37073859717421</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.34525724211998</v>
       </c>
       <c r="E98">
-        <v>-37.13793816531707</v>
+        <v>-38.41415044592173</v>
       </c>
       <c r="F98">
-        <v>-5.335220807080049</v>
+        <v>-4.158923238387399</v>
       </c>
       <c r="G98">
-        <v>-10.21782118816973</v>
+        <v>-11.58016364630845</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.26686136773247</v>
       </c>
       <c r="E99">
-        <v>-40.49726886758312</v>
+        <v>-40.78111588262091</v>
       </c>
       <c r="F99">
-        <v>-4.843693920634685</v>
+        <v>-4.47619179554513</v>
       </c>
       <c r="G99">
-        <v>-10.5827095175082</v>
+        <v>-10.61409017867495</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.20824661537127</v>
       </c>
       <c r="E100">
-        <v>-42.17364881082359</v>
+        <v>-42.8283959609856</v>
       </c>
       <c r="F100">
-        <v>-5.035939189856921</v>
+        <v>-4.227967273329855</v>
       </c>
       <c r="G100">
-        <v>-11.76272368007156</v>
+        <v>-10.92693342159054</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.06911671441791</v>
       </c>
       <c r="E101">
-        <v>-44.36602798910505</v>
+        <v>-44.79776364404833</v>
       </c>
       <c r="F101">
-        <v>-4.6727178218568</v>
+        <v>-4.14230303665782</v>
       </c>
       <c r="G101">
-        <v>-10.74101649465061</v>
+        <v>-12.07227955126666</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.92445068771707</v>
       </c>
       <c r="E102">
-        <v>-47.85847092058957</v>
+        <v>-47.5565643512092</v>
       </c>
       <c r="F102">
-        <v>-4.674944512373908</v>
+        <v>-4.193520085963131</v>
       </c>
       <c r="G102">
-        <v>-10.76326336067451</v>
+        <v>-12.79572313632697</v>
       </c>
     </row>
   </sheetData>
